--- a/public/templates/residents_template.xlsx
+++ b/public/templates/residents_template.xlsx
@@ -32,8 +32,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="60" formatCode="00"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -64,8 +65,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="60" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -397,7 +399,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:F2"/>
+  <cols>
+    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="28.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="8.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
+    <col min="6" max="6" width="13.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -407,47 +417,41 @@
         <v>Email</v>
       </c>
       <c r="C1" t="str">
-        <v>Password</v>
+        <v>Phone</v>
       </c>
       <c r="D1" t="str">
-        <v>Phone</v>
+        <v>Block</v>
       </c>
       <c r="E1" t="str">
-        <v>Block</v>
+        <v>Floor Number</v>
       </c>
       <c r="F1" t="str">
-        <v>Floor Number</v>
-      </c>
-      <c r="G1" t="str">
         <v>Unit Number</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>John Doe</v>
+        <v>Rahul Sharma</v>
       </c>
       <c r="B2" t="str">
-        <v>john.doe@yopmail.com</v>
+        <v>rahul.sharma@yopmail.com</v>
       </c>
       <c r="C2" t="str">
-        <v>Password@123</v>
+        <v>9876543210</v>
       </c>
       <c r="D2" t="str">
-        <v>9876543210</v>
-      </c>
-      <c r="E2" t="str">
         <v>A</v>
       </c>
-      <c r="F2">
+      <c r="E2">
         <v>1</v>
       </c>
-      <c r="G2" t="str">
-        <v>01</v>
+      <c r="F2" s="1">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/templates/residents_template.xlsx
+++ b/public/templates/residents_template.xlsx
@@ -399,14 +399,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:G2"/>
   <cols>
-    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="28.83203125" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" customWidth="1"/>
-    <col min="4" max="4" width="8.83203125" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" customWidth="1"/>
-    <col min="6" max="6" width="13.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="22.83203125" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" customWidth="1"/>
+    <col min="6" max="6" width="15.83203125" customWidth="1"/>
+    <col min="7" max="7" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -420,38 +421,44 @@
         <v>Phone</v>
       </c>
       <c r="D1" t="str">
+        <v>Is Committee Member</v>
+      </c>
+      <c r="E1" t="str">
         <v>Block</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>Floor Number</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>Unit Number</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Rahul Sharma</v>
+        <v>Aarav Sharma</v>
       </c>
       <c r="B2" t="str">
-        <v>rahul.sharma@yopmail.com</v>
+        <v>aarav.sharma@example.com</v>
       </c>
       <c r="C2" t="str">
         <v>9876543210</v>
       </c>
       <c r="D2" t="str">
+        <v>No</v>
+      </c>
+      <c r="E2" t="str">
         <v>A</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>1</v>
       </c>
-      <c r="F2" s="1">
+      <c r="G2" s="1">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
   </ignoredErrors>
 </worksheet>
 </file>